--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="7"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="tm_teacher" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="200">
   <si>
     <t>表名</t>
   </si>
@@ -140,493 +140,496 @@
     <t>jpa_version</t>
   </si>
   <si>
+    <t>///@javaVersion;///@optimisticlock</t>
+  </si>
+  <si>
+    <t>create_time</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>///@create</t>
+  </si>
+  <si>
+    <t>last_update_time</t>
+  </si>
+  <si>
+    <t>///@update</t>
+  </si>
+  <si>
+    <t>主键</t>
+  </si>
+  <si>
+    <t>PRIMARY_KEY</t>
+  </si>
+  <si>
+    <t>约束</t>
+  </si>
+  <si>
+    <t>tm_teacher_name_IDX</t>
+  </si>
+  <si>
+    <t>tm_teacher_phone_IDX</t>
+  </si>
+  <si>
+    <t>索引</t>
+  </si>
+  <si>
+    <t>tm_teacher_classid_IDX</t>
+  </si>
+  <si>
+    <t>tm_teacher_Name_IDX</t>
+  </si>
+  <si>
+    <t>方法名字</t>
+  </si>
+  <si>
+    <t>查询列</t>
+  </si>
+  <si>
+    <t>聚合函数</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>检索条件</t>
+  </si>
+  <si>
+    <t>排序条件</t>
+  </si>
+  <si>
+    <t>分组条件</t>
+  </si>
+  <si>
+    <t>分页</t>
+  </si>
+  <si>
+    <t>数据库类型</t>
+  </si>
+  <si>
+    <t>FindByNameNadAddress</t>
+  </si>
+  <si>
+    <t>name,address,phone,class_id</t>
+  </si>
+  <si>
+    <t>name = @Name and address = @Address</t>
+  </si>
+  <si>
+    <t>FindByPhone</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>phone = @Phone</t>
+  </si>
+  <si>
+    <t>tbl_3ds_request</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>数据表自增长ID(@readonly@)</t>
+  </si>
+  <si>
+    <t>CLUSTER_ID</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>在线库集群ID(第一位：集群ID（使用1-9）；第二位：表ID（取值A/B）。@readonly@)</t>
+  </si>
+  <si>
+    <t>TRANSACTION_TYPE</t>
+  </si>
+  <si>
+    <t>交易类型(01-DCC预支付,02-消费,03-消费撤销,04-消费冲正，05-消费撤销冲正（暂不支持），06-预授权，07-预授权撤销，08-预授权冲正，09-预授权撤销冲正（暂不支持），10-预授权完成，11-预授权完成撤销，12-预授权完成冲正，13-预授权完成撤销冲正（暂不支持），14-账户验证，20-退货；50-交易状态查询，61-3DS认证初始化,62-3DS认证，63-3DS认证挑战；81-拒付，82-再请款，83-收费，84-付费,85-拒付撤销，86-再请款撤销，87-收单行收费，88-收单行付费；90-回响测试，91-签到，92-签退，93-密钥切换，94-RECON，95-风险报告，96-文本通知（或有）。@enumType=com.allinfinance.marcopolo.enums.TransactionType@)</t>
+  </si>
+  <si>
+    <t>ORDER_ID</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>商户交易订单号</t>
+  </si>
+  <si>
+    <t>GATEWAY_SERVICE_KEY</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>网关微服务ID，全局跟踪号的第一部分(IP:Port#微服务ID)</t>
+  </si>
+  <si>
+    <t>GLOBAL_TRACE_NO</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>全局跟踪号第二部分，也用于同步转异步Key(与网关ID配合使用，YYYYMMDDHHMMSSmmm+10序列号)</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t>FLD2(存储加密)</t>
+  </si>
+  <si>
+    <t>PROCESSING_CODE</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>FLD3</t>
+  </si>
+  <si>
+    <t>ORDER_AMOUNT</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>订单金额</t>
+  </si>
+  <si>
+    <t>TRANSACTION_AMOUNT</t>
+  </si>
+  <si>
+    <t>FLD4(精确到分)</t>
+  </si>
+  <si>
+    <t>BILLING_AMOUNT</t>
+  </si>
+  <si>
+    <t>FLD6(精确到分，DCC由收单行提供该金额)</t>
+  </si>
+  <si>
+    <t>TRANSMISSION_DATETIME</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>FLD7</t>
+  </si>
+  <si>
+    <t>CONVERSION_RATE_BILLING</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>FLD10(卡组织汇率表示方式，参考卡组织规范。DCC情况下该汇率由银行提供（为包括了上浮部分的实际汇率）)</t>
+  </si>
+  <si>
+    <t>STAN</t>
+  </si>
+  <si>
+    <t>FLD11</t>
+  </si>
+  <si>
+    <t>LOCAL_TIME</t>
+  </si>
+  <si>
+    <t>FLD12</t>
+  </si>
+  <si>
+    <t>LOCAL_DATE</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>FLD13</t>
+  </si>
+  <si>
+    <t>MCC</t>
+  </si>
+  <si>
+    <t>FLD18</t>
+  </si>
+  <si>
+    <t>ACQUIRING_INST_COUNTRY_CODE</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>FLD19</t>
+  </si>
+  <si>
+    <t>POS_ENTRY_MODE</t>
+  </si>
+  <si>
+    <t>FLD22</t>
+  </si>
+  <si>
+    <t>POS_CONDITION_CODE</t>
+  </si>
+  <si>
+    <t>FLD25</t>
+  </si>
+  <si>
+    <t>POS_PIN_CAPTURE_CODE</t>
+  </si>
+  <si>
+    <t>FLD26</t>
+  </si>
+  <si>
+    <t>ACQUIRING_INSTITUTION</t>
+  </si>
+  <si>
+    <t>FLD32</t>
+  </si>
+  <si>
+    <t>RETRIEVAL_REFERENCE_NUMBER</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>FLD37(最后一位是集群单元ID号)</t>
+  </si>
+  <si>
+    <t>TERMINAL_ID</t>
+  </si>
+  <si>
+    <t>FLD41</t>
+  </si>
+  <si>
+    <t>MERCHANT_ID</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>FLD42，厦门国际构成：2位机构号+3位分行号+4位MCC+后2位机构号4位商户序号或6位商户序号；其他行构成：4位分行号+4位MCC+4位机构号（首位不为9）|3位顺序号或9|6位顺序号</t>
+  </si>
+  <si>
+    <t>CARD_ACCEPTOR_LOCATION</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>FLD43</t>
+  </si>
+  <si>
+    <t>ORDER_CURRENCY</t>
+  </si>
+  <si>
+    <t>订单币种(联机参数)</t>
+  </si>
+  <si>
+    <t>TRANSACTION_CURRENCY</t>
+  </si>
+  <si>
+    <t>FLD49(考虑境外外卡收单场景，该字段可能不为156)</t>
+  </si>
+  <si>
+    <t>BILLING_CURRENCY</t>
+  </si>
+  <si>
+    <t>FLD51</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_POS_DATA</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>FLD60/DE61(VISA长度12，MC长度26)</t>
+  </si>
+  <si>
+    <t>CARD_TYPE</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>卡片类型(V-VISA；M-MC；J-JCB；A-AMEX；D-DC；C-CUP。@enumType=com.allinfinance.marcopolo.enums.CardType@)</t>
+  </si>
+  <si>
+    <t>DCC_FLAG</t>
+  </si>
+  <si>
+    <t>DCC标记(1-DCC交易；0-非DCC交易。@enumType=com.allinfinance.marcopolo.enums.DccFlag@)</t>
+  </si>
+  <si>
+    <t>KEY_DATETIME</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>加密存储数据时的密钥版本(YYYYMMDDHHMMSS)</t>
+  </si>
+  <si>
+    <t>DEVICE_TYPE</t>
+  </si>
+  <si>
+    <t>设备备注字段(取值: WEB/ANDROID/IOS/CONSOLE等。@enumType=com.allinfinance.marcopolo.enums.DeviceType@)</t>
+  </si>
+  <si>
+    <t>INTERFACE_VERSION</t>
+  </si>
+  <si>
+    <t>商户接口版本(取值：O1.0/O1.1/P1.0等 O代表线上，P代表线下)</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>终端或持卡人浏览器IP地址(支持IP4和IP6，备注字段)</t>
+  </si>
+  <si>
+    <t>RISK_SERVICE_FLAG</t>
+  </si>
+  <si>
+    <t>商户上送的风险评估服务标记(0-不使用，1-使用。老系统必须取值1。@enumType=com.allinfinance.marcopolo.enums.RiskServiceFlag@)</t>
+  </si>
+  <si>
+    <t>PAYMENT_TYPE</t>
+  </si>
+  <si>
+    <t>支付类型(0-线下，1-Normal E-Commerce,2-3DS ,4- 控台手工发起。@enumType=com.allinfinance.marcopolo.enums.PaymentType@)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_COUNTRY</t>
+  </si>
+  <si>
+    <t>持卡人国籍(2位国家字母简写)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_ADDRESS</t>
+  </si>
+  <si>
+    <t>250</t>
+  </si>
+  <si>
+    <t>持卡人地址</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_NAME</t>
+  </si>
+  <si>
+    <t>持卡人名称(加密存放)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_STATE</t>
+  </si>
+  <si>
+    <t>持卡人州省(需要符合ISO3166-2中State-code)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_CITY</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>持卡人城市</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_ZIP_CODE</t>
+  </si>
+  <si>
+    <t>持卡人邮编</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_PHONE</t>
+  </si>
+  <si>
+    <t>持卡人电话(加密存放)</t>
+  </si>
+  <si>
+    <t>CARDHOLDER_EMAIL</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>持卡人EMAIL(加密存放)</t>
+  </si>
+  <si>
+    <t>RESERVED_1</t>
+  </si>
+  <si>
+    <t>保留字段1</t>
+  </si>
+  <si>
+    <t>RESERVED_2</t>
+  </si>
+  <si>
+    <t>保留字段2</t>
+  </si>
+  <si>
+    <t>INSERT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP(6)</t>
+  </si>
+  <si>
+    <t>记录创建时间戳</t>
+  </si>
+  <si>
+    <t>INSERT_USER</t>
+  </si>
+  <si>
+    <t>记录创建人(用户名或程序名)</t>
+  </si>
+  <si>
+    <t>IDX_RRN</t>
+  </si>
+  <si>
+    <t>IDX_INSERT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>IDX_ORDER_ID</t>
+  </si>
+  <si>
+    <t>Xxxxx</t>
+  </si>
+  <si>
+    <t>RETRIEVAL_REFERENCE_NUMBER = @RRN</t>
+  </si>
+  <si>
+    <t>tm_student</t>
+  </si>
+  <si>
+    <t>tenant_id</t>
+  </si>
+  <si>
+    <t>student_no</t>
+  </si>
+  <si>
+    <t>score</t>
+  </si>
+  <si>
+    <t>enroll_date</t>
+  </si>
+  <si>
+    <t>is_graduate</t>
+  </si>
+  <si>
     <t>///@javaVersion</t>
-  </si>
-  <si>
-    <t>create_time</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>///@create</t>
-  </si>
-  <si>
-    <t>last_update_time</t>
-  </si>
-  <si>
-    <t>///@update</t>
-  </si>
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>PRIMARY_KEY</t>
-  </si>
-  <si>
-    <t>约束</t>
-  </si>
-  <si>
-    <t>tm_teacher_name_IDX</t>
-  </si>
-  <si>
-    <t>tm_teacher_phone_IDX</t>
-  </si>
-  <si>
-    <t>索引</t>
-  </si>
-  <si>
-    <t>tm_teacher_classid_IDX</t>
-  </si>
-  <si>
-    <t>tm_teacher_Name_IDX</t>
-  </si>
-  <si>
-    <t>方法名字</t>
-  </si>
-  <si>
-    <t>查询列</t>
-  </si>
-  <si>
-    <t>聚合函数</t>
-  </si>
-  <si>
-    <t>类型</t>
-  </si>
-  <si>
-    <t>检索条件</t>
-  </si>
-  <si>
-    <t>排序条件</t>
-  </si>
-  <si>
-    <t>分组条件</t>
-  </si>
-  <si>
-    <t>分页</t>
-  </si>
-  <si>
-    <t>数据库类型</t>
-  </si>
-  <si>
-    <t>FindByNameNadAddress</t>
-  </si>
-  <si>
-    <t>name,address,phone,class_id</t>
-  </si>
-  <si>
-    <t>name = @Name and address = @Address</t>
-  </si>
-  <si>
-    <t>FindByPhone</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>phone = @Phone</t>
-  </si>
-  <si>
-    <t>tbl_3ds_request</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>数据表自增长ID(@readonly@)</t>
-  </si>
-  <si>
-    <t>CLUSTER_ID</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>在线库集群ID(第一位：集群ID（使用1-9）；第二位：表ID（取值A/B）。@readonly@)</t>
-  </si>
-  <si>
-    <t>TRANSACTION_TYPE</t>
-  </si>
-  <si>
-    <t>交易类型(01-DCC预支付,02-消费,03-消费撤销,04-消费冲正，05-消费撤销冲正（暂不支持），06-预授权，07-预授权撤销，08-预授权冲正，09-预授权撤销冲正（暂不支持），10-预授权完成，11-预授权完成撤销，12-预授权完成冲正，13-预授权完成撤销冲正（暂不支持），14-账户验证，20-退货；50-交易状态查询，61-3DS认证初始化,62-3DS认证，63-3DS认证挑战；81-拒付，82-再请款，83-收费，84-付费,85-拒付撤销，86-再请款撤销，87-收单行收费，88-收单行付费；90-回响测试，91-签到，92-签退，93-密钥切换，94-RECON，95-风险报告，96-文本通知（或有）。@enumType=com.allinfinance.marcopolo.enums.TransactionType@)</t>
-  </si>
-  <si>
-    <t>ORDER_ID</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>商户交易订单号</t>
-  </si>
-  <si>
-    <t>GATEWAY_SERVICE_KEY</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>网关微服务ID，全局跟踪号的第一部分(IP:Port#微服务ID)</t>
-  </si>
-  <si>
-    <t>GLOBAL_TRACE_NO</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>全局跟踪号第二部分，也用于同步转异步Key(与网关ID配合使用，YYYYMMDDHHMMSSmmm+10序列号)</t>
-  </si>
-  <si>
-    <t>PAN</t>
-  </si>
-  <si>
-    <t>FLD2(存储加密)</t>
-  </si>
-  <si>
-    <t>PROCESSING_CODE</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>FLD3</t>
-  </si>
-  <si>
-    <t>ORDER_AMOUNT</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>订单金额</t>
-  </si>
-  <si>
-    <t>TRANSACTION_AMOUNT</t>
-  </si>
-  <si>
-    <t>FLD4(精确到分)</t>
-  </si>
-  <si>
-    <t>BILLING_AMOUNT</t>
-  </si>
-  <si>
-    <t>FLD6(精确到分，DCC由收单行提供该金额)</t>
-  </si>
-  <si>
-    <t>TRANSMISSION_DATETIME</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>FLD7</t>
-  </si>
-  <si>
-    <t>CONVERSION_RATE_BILLING</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>FLD10(卡组织汇率表示方式，参考卡组织规范。DCC情况下该汇率由银行提供（为包括了上浮部分的实际汇率）)</t>
-  </si>
-  <si>
-    <t>STAN</t>
-  </si>
-  <si>
-    <t>FLD11</t>
-  </si>
-  <si>
-    <t>LOCAL_TIME</t>
-  </si>
-  <si>
-    <t>FLD12</t>
-  </si>
-  <si>
-    <t>LOCAL_DATE</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>FLD13</t>
-  </si>
-  <si>
-    <t>MCC</t>
-  </si>
-  <si>
-    <t>FLD18</t>
-  </si>
-  <si>
-    <t>ACQUIRING_INST_COUNTRY_CODE</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>FLD19</t>
-  </si>
-  <si>
-    <t>POS_ENTRY_MODE</t>
-  </si>
-  <si>
-    <t>FLD22</t>
-  </si>
-  <si>
-    <t>POS_CONDITION_CODE</t>
-  </si>
-  <si>
-    <t>FLD25</t>
-  </si>
-  <si>
-    <t>POS_PIN_CAPTURE_CODE</t>
-  </si>
-  <si>
-    <t>FLD26</t>
-  </si>
-  <si>
-    <t>ACQUIRING_INSTITUTION</t>
-  </si>
-  <si>
-    <t>FLD32</t>
-  </si>
-  <si>
-    <t>RETRIEVAL_REFERENCE_NUMBER</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>FLD37(最后一位是集群单元ID号)</t>
-  </si>
-  <si>
-    <t>TERMINAL_ID</t>
-  </si>
-  <si>
-    <t>FLD41</t>
-  </si>
-  <si>
-    <t>MERCHANT_ID</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>FLD42，厦门国际构成：2位机构号+3位分行号+4位MCC+后2位机构号4位商户序号或6位商户序号；其他行构成：4位分行号+4位MCC+4位机构号（首位不为9）|3位顺序号或9|6位顺序号</t>
-  </si>
-  <si>
-    <t>CARD_ACCEPTOR_LOCATION</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>FLD43</t>
-  </si>
-  <si>
-    <t>ORDER_CURRENCY</t>
-  </si>
-  <si>
-    <t>订单币种(联机参数)</t>
-  </si>
-  <si>
-    <t>TRANSACTION_CURRENCY</t>
-  </si>
-  <si>
-    <t>FLD49(考虑境外外卡收单场景，该字段可能不为156)</t>
-  </si>
-  <si>
-    <t>BILLING_CURRENCY</t>
-  </si>
-  <si>
-    <t>FLD51</t>
-  </si>
-  <si>
-    <t>ADDITIONAL_POS_DATA</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>FLD60/DE61(VISA长度12，MC长度26)</t>
-  </si>
-  <si>
-    <t>CARD_TYPE</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>卡片类型(V-VISA；M-MC；J-JCB；A-AMEX；D-DC；C-CUP。@enumType=com.allinfinance.marcopolo.enums.CardType@)</t>
-  </si>
-  <si>
-    <t>DCC_FLAG</t>
-  </si>
-  <si>
-    <t>DCC标记(1-DCC交易；0-非DCC交易。@enumType=com.allinfinance.marcopolo.enums.DccFlag@)</t>
-  </si>
-  <si>
-    <t>KEY_DATETIME</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>加密存储数据时的密钥版本(YYYYMMDDHHMMSS)</t>
-  </si>
-  <si>
-    <t>DEVICE_TYPE</t>
-  </si>
-  <si>
-    <t>设备备注字段(取值: WEB/ANDROID/IOS/CONSOLE等。@enumType=com.allinfinance.marcopolo.enums.DeviceType@)</t>
-  </si>
-  <si>
-    <t>INTERFACE_VERSION</t>
-  </si>
-  <si>
-    <t>商户接口版本(取值：O1.0/O1.1/P1.0等 O代表线上，P代表线下)</t>
-  </si>
-  <si>
-    <t>IP</t>
-  </si>
-  <si>
-    <t>终端或持卡人浏览器IP地址(支持IP4和IP6，备注字段)</t>
-  </si>
-  <si>
-    <t>RISK_SERVICE_FLAG</t>
-  </si>
-  <si>
-    <t>商户上送的风险评估服务标记(0-不使用，1-使用。老系统必须取值1。@enumType=com.allinfinance.marcopolo.enums.RiskServiceFlag@)</t>
-  </si>
-  <si>
-    <t>PAYMENT_TYPE</t>
-  </si>
-  <si>
-    <t>支付类型(0-线下，1-Normal E-Commerce,2-3DS ,4- 控台手工发起。@enumType=com.allinfinance.marcopolo.enums.PaymentType@)</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_COUNTRY</t>
-  </si>
-  <si>
-    <t>持卡人国籍(2位国家字母简写)</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_ADDRESS</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>持卡人地址</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_NAME</t>
-  </si>
-  <si>
-    <t>持卡人名称(加密存放)</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_STATE</t>
-  </si>
-  <si>
-    <t>持卡人州省(需要符合ISO3166-2中State-code)</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_CITY</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>持卡人城市</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_ZIP_CODE</t>
-  </si>
-  <si>
-    <t>持卡人邮编</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_PHONE</t>
-  </si>
-  <si>
-    <t>持卡人电话(加密存放)</t>
-  </si>
-  <si>
-    <t>CARDHOLDER_EMAIL</t>
-  </si>
-  <si>
-    <t>128</t>
-  </si>
-  <si>
-    <t>持卡人EMAIL(加密存放)</t>
-  </si>
-  <si>
-    <t>RESERVED_1</t>
-  </si>
-  <si>
-    <t>保留字段1</t>
-  </si>
-  <si>
-    <t>RESERVED_2</t>
-  </si>
-  <si>
-    <t>保留字段2</t>
-  </si>
-  <si>
-    <t>INSERT_TIMESTAMP</t>
-  </si>
-  <si>
-    <t>CURRENT_TIMESTAMP(6)</t>
-  </si>
-  <si>
-    <t>记录创建时间戳</t>
-  </si>
-  <si>
-    <t>INSERT_USER</t>
-  </si>
-  <si>
-    <t>记录创建人(用户名或程序名)</t>
-  </si>
-  <si>
-    <t>IDX_RRN</t>
-  </si>
-  <si>
-    <t>IDX_INSERT_TIMESTAMP</t>
-  </si>
-  <si>
-    <t>IDX_ORDER_ID</t>
-  </si>
-  <si>
-    <t>Xxxxx</t>
-  </si>
-  <si>
-    <t>RETRIEVAL_REFERENCE_NUMBER = @RRN</t>
-  </si>
-  <si>
-    <t>tm_student</t>
-  </si>
-  <si>
-    <t>tenant_id</t>
-  </si>
-  <si>
-    <t>student_no</t>
-  </si>
-  <si>
-    <t>score</t>
-  </si>
-  <si>
-    <t>enroll_date</t>
-  </si>
-  <si>
-    <t>is_graduate</t>
   </si>
   <si>
     <t>tm_no_primary</t>
@@ -4846,7 +4849,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5277,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5587,7 +5590,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -5989,7 +5992,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6299,7 +6302,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -6614,7 +6617,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6924,7 +6927,7 @@
         <v>13</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>33</v>
+        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:9">

--- a/tool/cmd/gen-go-db/test_20260626.xlsx
+++ b/tool/cmd/gen-go-db/test_20260626.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai-workspace\ag-core\tool\cmd\gen-go-db\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="12375" windowWidth="27945"/>
   </bookViews>
   <sheets>
-    <sheet name="tm_teacher" sheetId="2" r:id="rId1"/>
-    <sheet name="tm_teacher@" sheetId="3" r:id="rId2"/>
-    <sheet name="tbl_3ds_request" sheetId="4" r:id="rId3"/>
-    <sheet name="tbl_3ds_request@" sheetId="5" r:id="rId4"/>
-    <sheet name="tm_student" sheetId="6" r:id="rId5"/>
-    <sheet name="tm_no_primary" sheetId="7" r:id="rId6"/>
-    <sheet name="tm_no_index" sheetId="8" r:id="rId7"/>
-    <sheet name="tm_no" sheetId="9" r:id="rId8"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_teacher" sheetId="2" relationships:id="rId1"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_teacher@" sheetId="3" relationships:id="rId2"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tbl_3ds_request" sheetId="4" relationships:id="rId3"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tbl_3ds_request@" sheetId="5" relationships:id="rId4"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_student" sheetId="6" relationships:id="rId5"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_no_primary" sheetId="7" relationships:id="rId6"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_no_index" sheetId="8" relationships:id="rId7"/>
+    <sheet xmlns:relationships="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tm_no" sheetId="9" relationships:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -644,7 +639,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -819,10 +814,16 @@
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <fgColor/>
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <fgColor/>
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1134,209 +1135,209 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="43">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="44">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="41">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="42">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="3" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="4" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="2" fillId="2" fontId="0" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="5" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="6" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="7" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="8" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="3" fillId="0" fontId="9" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="4" fillId="0" fontId="10" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="10" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="3" fontId="11" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="6" fillId="4" fontId="12" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="5" fillId="4" fontId="13" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="7" fillId="5" fontId="14" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="8" fillId="0" fontId="15" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="9" fillId="0" fontId="16" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="6" fontId="17" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="7" fontId="18" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="8" fontId="19" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="9" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="10" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="11" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="12" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="13" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="14" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="15" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="16" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="17" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="18" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="19" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="20" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="21" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="22" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="23" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="24" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="25" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="26" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="27" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="28" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="29" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="30" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="31" fontId="21" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="32" fontId="20" numFmtId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="false" applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="false" applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle builtinId="0" name="常规" xfId="0"/>
+    <cellStyle builtinId="3" name="千位分隔" xfId="1"/>
+    <cellStyle builtinId="4" name="货币" xfId="2"/>
+    <cellStyle builtinId="5" name="百分比" xfId="3"/>
+    <cellStyle builtinId="6" name="千位分隔[0]" xfId="4"/>
+    <cellStyle builtinId="7" name="货币[0]" xfId="5"/>
+    <cellStyle builtinId="8" name="超链接" xfId="6"/>
+    <cellStyle builtinId="9" name="已访问的超链接" xfId="7"/>
+    <cellStyle builtinId="10" name="注释" xfId="8"/>
+    <cellStyle builtinId="11" name="警告文本" xfId="9"/>
+    <cellStyle builtinId="15" name="标题" xfId="10"/>
+    <cellStyle builtinId="53" name="解释性文本" xfId="11"/>
+    <cellStyle builtinId="16" name="标题 1" xfId="12"/>
+    <cellStyle builtinId="17" name="标题 2" xfId="13"/>
+    <cellStyle builtinId="18" name="标题 3" xfId="14"/>
+    <cellStyle builtinId="19" name="标题 4" xfId="15"/>
+    <cellStyle builtinId="20" name="输入" xfId="16"/>
+    <cellStyle builtinId="21" name="输出" xfId="17"/>
+    <cellStyle builtinId="22" name="计算" xfId="18"/>
+    <cellStyle builtinId="23" name="检查单元格" xfId="19"/>
+    <cellStyle builtinId="24" name="链接单元格" xfId="20"/>
+    <cellStyle builtinId="25" name="汇总" xfId="21"/>
+    <cellStyle builtinId="26" name="好" xfId="22"/>
+    <cellStyle builtinId="27" name="差" xfId="23"/>
+    <cellStyle builtinId="28" name="适中" xfId="24"/>
+    <cellStyle builtinId="29" name="强调文字颜色 1" xfId="25"/>
+    <cellStyle builtinId="30" name="20% - 强调文字颜色 1" xfId="26"/>
+    <cellStyle builtinId="31" name="40% - 强调文字颜色 1" xfId="27"/>
+    <cellStyle builtinId="32" name="60% - 强调文字颜色 1" xfId="28"/>
+    <cellStyle builtinId="33" name="强调文字颜色 2" xfId="29"/>
+    <cellStyle builtinId="34" name="20% - 强调文字颜色 2" xfId="30"/>
+    <cellStyle builtinId="35" name="40% - 强调文字颜色 2" xfId="31"/>
+    <cellStyle builtinId="36" name="60% - 强调文字颜色 2" xfId="32"/>
+    <cellStyle builtinId="37" name="强调文字颜色 3" xfId="33"/>
+    <cellStyle builtinId="38" name="20% - 强调文字颜色 3" xfId="34"/>
+    <cellStyle builtinId="39" name="40% - 强调文字颜色 3" xfId="35"/>
+    <cellStyle builtinId="40" name="60% - 强调文字颜色 3" xfId="36"/>
+    <cellStyle builtinId="41" name="强调文字颜色 4" xfId="37"/>
+    <cellStyle builtinId="42" name="20% - 强调文字颜色 4" xfId="38"/>
+    <cellStyle builtinId="43" name="40% - 强调文字颜色 4" xfId="39"/>
+    <cellStyle builtinId="44" name="60% - 强调文字颜色 4" xfId="40"/>
+    <cellStyle builtinId="45" name="强调文字颜色 5" xfId="41"/>
+    <cellStyle builtinId="46" name="20% - 强调文字颜色 5" xfId="42"/>
+    <cellStyle builtinId="47" name="40% - 强调文字颜色 5" xfId="43"/>
+    <cellStyle builtinId="48" name="60% - 强调文字颜色 5" xfId="44"/>
+    <cellStyle builtinId="49" name="强调文字颜色 6" xfId="45"/>
+    <cellStyle builtinId="50" name="20% - 强调文字颜色 6" xfId="46"/>
+    <cellStyle builtinId="51" name="40% - 强调文字颜色 6" xfId="47"/>
+    <cellStyle builtinId="52" name="60% - 强调文字颜色 6" xfId="48"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1601,14 +1602,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.6666666666667" customWidth="1"/>
-    <col min="2" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="14.6666666666667"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1855,8 +1856,8 @@
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>29</v>
+      <c r="B10" s="2" t="str">
+        <v>*time</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2317,22 +2318,22 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="13.3333333333333" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="23.3333333333333" customWidth="1"/>
-    <col min="6" max="9" width="15" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="13.3333333333333"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="4" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="23.3333333333333"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="6" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2423,25 +2424,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:J63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="17.3333333333333" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="13.3333333333333" customWidth="1"/>
-    <col min="6" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="2" min="2" style="0" width="17.3333333333333"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="4" min="4" style="0" width="10.6666666666667"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="13.3333333333333"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="7" min="6" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="8" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4437,20 +4438,20 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="9" width="15" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="4" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="6" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4518,23 +4519,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32.875"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="21.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row customFormat="true" r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4797,8 +4798,8 @@
       <c r="A11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
+      <c r="B11" s="2" t="str">
+        <v>*time</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -5259,23 +5260,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32.875"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="21.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row customFormat="true" r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5538,8 +5539,8 @@
       <c r="A11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
+      <c r="B11" s="2" t="str">
+        <v>*time</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -5971,23 +5972,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32.875"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="21.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row customFormat="true" r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6250,8 +6251,8 @@
       <c r="A11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
+      <c r="B11" s="2" t="str">
+        <v>*time</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -6596,23 +6597,23 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr/>
   <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="32.875" customWidth="1"/>
-    <col min="2" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="21.75" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="1" min="1" style="0" width="32.875"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="8" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" max="9" min="9" style="0" width="21.75"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:9">
+    <row customFormat="true" r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6875,8 +6876,8 @@
       <c r="A11" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
+      <c r="B11" s="2" t="str">
+        <v>*time</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -7192,7 +7193,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
   <headerFooter/>
 </worksheet>
 </file>